--- a/Insumo/EnvioCorreos.xlsx
+++ b/Insumo/EnvioCorreos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.50.169\RPA_Pricingmedicamentos\Insumo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netapplicationscomco-my.sharepoint.com/personal/paula_sierra_netapplications_com_co/Documents/Documentos/Colsubsidio/ShoppingDePrecios/Insumo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC1E6E8-B1BD-429A-B080-8379A4CC1939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{2DC1E6E8-B1BD-429A-B080-8379A4CC1939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{046410BB-F313-495E-A9F9-4AD908F5E952}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{DA173E89-5736-462B-8092-2DA4EDEA5531}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DA173E89-5736-462B-8092-2DA4EDEA5531}"/>
   </bookViews>
   <sheets>
     <sheet name="EnvioCorreos" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
   <si>
     <t>IdCorreo</t>
   </si>
@@ -212,10 +212,7 @@
 Muchas gracias.</t>
   </si>
   <si>
-    <t>jamebarrub@colsubsidio.com</t>
-  </si>
-  <si>
-    <t>jamebarrub@colsubsidio.com;sonimadr@colsubsidio.com;joseojma@colsubsidio.com;viviana.osorio@colsubsidio.com;renebersan@colsubsidio.com;anyhbaeama@colsubsidio.com</t>
+    <t>paula.sierra@netapplications.com.co</t>
   </si>
 </sst>
 </file>
@@ -738,17 +735,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6253738D-CA41-40B7-A6BB-F72FD2BB4964}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="20.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="20.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.453125" customWidth="1"/>
-    <col min="3" max="3" width="23.81640625" customWidth="1"/>
-    <col min="4" max="4" width="20.54296875" customWidth="1"/>
-    <col min="5" max="5" width="40.26953125" customWidth="1"/>
-    <col min="6" max="6" width="41.7265625" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" customWidth="1"/>
+    <col min="3" max="3" width="23.77734375" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" customWidth="1"/>
+    <col min="5" max="5" width="40.21875" customWidth="1"/>
+    <col min="6" max="6" width="41.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="14" thickBot="1">
+    <row r="1" spans="1:7" s="1" customFormat="1" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -771,7 +768,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="87">
+    <row r="2" spans="1:7" ht="86.4">
       <c r="A2" s="5">
         <v>0</v>
       </c>
@@ -790,7 +787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="130.5">
+    <row r="3" spans="1:7" ht="115.2">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -809,7 +806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="145">
+    <row r="4" spans="1:7" ht="129.6">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -828,7 +825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="116">
+    <row r="5" spans="1:7" ht="100.8">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -847,7 +844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="159.5">
+    <row r="6" spans="1:7" ht="158.4">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -871,7 +868,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -885,7 +882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="409.5">
+    <row r="8" spans="1:7" ht="409.6">
       <c r="A8" s="5">
         <v>11</v>
       </c>
@@ -904,7 +901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="130.5">
+    <row r="9" spans="1:7" ht="129.6">
       <c r="A9" s="5">
         <v>99</v>
       </c>
@@ -923,7 +920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="116">
+    <row r="10" spans="1:7" ht="100.8">
       <c r="A10" s="5">
         <v>100</v>
       </c>
@@ -983,7 +980,7 @@
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{C5CB0F2E-960F-4F46-94BF-B08BCAE98AEE}"/>
     <hyperlink ref="C3:C10" r:id="rId2" display="jpgarzon@kpmg.com" xr:uid="{0FDD7636-FEAF-4A49-A5C0-12653D2FD050}"/>
-    <hyperlink ref="B7" r:id="rId3" xr:uid="{D15ACDB0-6C4E-4EC6-A351-5CE1509863EA}"/>
+    <hyperlink ref="B3:B10" r:id="rId3" display="paula.sierra@netapplications.com.co" xr:uid="{443CE30C-85FA-4AB1-9A0B-C1EB0AF0D64C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId4"/>
@@ -997,20 +994,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1cf10ad6-e21a-4e58-9416-642e0dfe1e20">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f4d28841-0b63-4903-af37-f70459a101b1" xsi:nil="true"/>
-    <Hipervinculo xmlns="1cf10ad6-e21a-4e58-9416-642e0dfe1e20">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Hipervinculo>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1287,22 +1276,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1cf10ad6-e21a-4e58-9416-642e0dfe1e20">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f4d28841-0b63-4903-af37-f70459a101b1" xsi:nil="true"/>
+    <Hipervinculo xmlns="1cf10ad6-e21a-4e58-9416-642e0dfe1e20">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Hipervinculo>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{539970DD-C4CE-4B7E-8E47-2390DADABE64}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F47D8A6-4B7B-40AF-BEC3-196CBDB18F6E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="1cf10ad6-e21a-4e58-9416-642e0dfe1e20"/>
-    <ds:schemaRef ds:uri="f4d28841-0b63-4903-af37-f70459a101b1"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1328,9 +1321,13 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F47D8A6-4B7B-40AF-BEC3-196CBDB18F6E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{539970DD-C4CE-4B7E-8E47-2390DADABE64}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="1cf10ad6-e21a-4e58-9416-642e0dfe1e20"/>
+    <ds:schemaRef ds:uri="f4d28841-0b63-4903-af37-f70459a101b1"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
